--- a/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationReplenishExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationReplenishExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>SKU</t>
   </si>
@@ -58,19 +58,25 @@
     <t>{.skuNo}</t>
   </si>
   <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
     <t>{.warehouseName}</t>
   </si>
   <si>
-    <t>{.status}</t>
-  </si>
-  <si>
-    <t>{.createUser}</t>
+    <t>{.suggestQty}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
   </si>
   <si>
-    <t>{.updateUser}</t>
+    <t>{.updateUserName}</t>
   </si>
 </sst>
 </file>
@@ -1055,21 +1061,26 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2"/>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationReplenishExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/warehouseLocationReplenishExport.xlsx
@@ -29,54 +29,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>SKU</t>
   </si>
   <si>
+    <t>补货类型</t>
+  </si>
+  <si>
     <t>来源单号</t>
   </si>
   <si>
     <t>仓库</t>
   </si>
   <si>
-    <t>缺货数量</t>
+    <t>推荐取货库区</t>
+  </si>
+  <si>
+    <t>推荐取货仓位</t>
+  </si>
+  <si>
+    <t>建议补货数量</t>
+  </si>
+  <si>
+    <t>推荐补货库区</t>
+  </si>
+  <si>
+    <t>推荐补货仓位</t>
+  </si>
+  <si>
+    <t>实际补货数量</t>
   </si>
   <si>
     <t>单据状态</t>
   </si>
   <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
-    <t>处理人</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
+    <t>{.sourceTypeName}</t>
+  </si>
+  <si>
     <t>{.sourceCode}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>
   </si>
   <si>
+    <t>{.fromWarehouseAreaName}</t>
+  </si>
+  <si>
+    <t>{.fromWarehouseLocationName}</t>
+  </si>
+  <si>
     <t>{.suggestQty}</t>
   </si>
   <si>
+    <t>{.toWarehouseAreaName}</t>
+  </si>
+  <si>
+    <t>{.toWarehouseLocationName}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
     <t>{.statusName}</t>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.updateUserName}</t>
   </si>
 </sst>
 </file>
@@ -89,8 +107,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -570,142 +596,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1018,69 +1050,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="4" width="12.125" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="19.375" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="20.125" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="13.75" customWidth="1"/>
+    <col min="14" max="14" width="19.375" customWidth="1"/>
+    <col min="15" max="15" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="17" customHeight="1" spans="1:15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
